--- a/Result/21-12-24/HKEXstock_21-12-24period60RS80.xlsx
+++ b/Result/21-12-24/HKEXstock_21-12-24period60RS80.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/21-12-24/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3A06F7-0B69-1A4E-A63A-93EDDCF94AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -148,144 +142,144 @@
     <t>3888.HK</t>
   </si>
   <si>
+    <t>3323.HK</t>
+  </si>
+  <si>
+    <t>1810.HK</t>
+  </si>
+  <si>
+    <t>2400.HK</t>
+  </si>
+  <si>
+    <t>1478.HK</t>
+  </si>
+  <si>
+    <t>3978.HK</t>
+  </si>
+  <si>
+    <t>2268.HK</t>
+  </si>
+  <si>
+    <t>9961.HK</t>
+  </si>
+  <si>
+    <t>1928.HK</t>
+  </si>
+  <si>
+    <t>2382.HK</t>
+  </si>
+  <si>
+    <t>1070.HK</t>
+  </si>
+  <si>
+    <t>6100.HK</t>
+  </si>
+  <si>
+    <t>0780.HK</t>
+  </si>
+  <si>
+    <t>6099.HK</t>
+  </si>
+  <si>
+    <t>9896.HK</t>
+  </si>
+  <si>
+    <t>3933.HK</t>
+  </si>
+  <si>
+    <t>0285.HK</t>
+  </si>
+  <si>
     <t>2025-03-18</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>2025-03-17</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
     <t>Communication Services</t>
   </si>
   <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
     <t>Electronic Gaming &amp; Multimedia</t>
   </si>
   <si>
-    <t>3323.HK</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
     <t>Building Materials</t>
   </si>
   <si>
-    <t>1810.HK</t>
-  </si>
-  <si>
-    <t>2025-03-17</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
     <t>Consumer Electronics</t>
   </si>
   <si>
-    <t>2400.HK</t>
-  </si>
-  <si>
-    <t>1478.HK</t>
-  </si>
-  <si>
     <t>Electronic Components</t>
   </si>
   <si>
-    <t>3978.HK</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
     <t>Education &amp; Training Services</t>
   </si>
   <si>
-    <t>2268.HK</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
     <t>Diagnostics &amp; Research</t>
   </si>
   <si>
-    <t>9961.HK</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
     <t>Travel Services</t>
   </si>
   <si>
-    <t>1928.HK</t>
-  </si>
-  <si>
-    <t>2025-02-14</t>
-  </si>
-  <si>
     <t>Resorts &amp; Casinos</t>
   </si>
   <si>
-    <t>2382.HK</t>
-  </si>
-  <si>
-    <t>1070.HK</t>
-  </si>
-  <si>
-    <t>6100.HK</t>
-  </si>
-  <si>
-    <t>2025-03-20</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
     <t>Staffing &amp; Employment Services</t>
   </si>
   <si>
-    <t>0780.HK</t>
-  </si>
-  <si>
-    <t>6099.HK</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
     <t>Capital Markets</t>
   </si>
   <si>
-    <t>9896.HK</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
     <t>Specialty Retail</t>
   </si>
   <si>
-    <t>3933.HK</t>
-  </si>
-  <si>
     <t>Drug Manufacturers - Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>0285.HK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -293,54 +287,17 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="新細明體"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFA500"/>
-        <bgColor rgb="FFFFA500"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -370,30 +327,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -681,9 +625,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AO18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
@@ -815,7 +759,7 @@
         <v>41</v>
       </c>
       <c r="B2">
-        <v>88.037735849056602</v>
+        <v>88.0377358490566</v>
       </c>
       <c r="C2">
         <v>259</v>
@@ -826,23 +770,23 @@
       <c r="E2">
         <v>2.09</v>
       </c>
-      <c r="F2" s="2">
-        <v>-1.0572131297755569</v>
+      <c r="F2">
+        <v>-1.057213129775557</v>
       </c>
       <c r="G2">
         <v>4.26</v>
       </c>
       <c r="H2">
-        <v>-0.28970396241757163</v>
+        <v>-0.2897039624175716</v>
       </c>
       <c r="I2">
-        <v>34.019999694824222</v>
+        <v>34.01999969482422</v>
       </c>
       <c r="J2">
-        <v>32.827500057220462</v>
+        <v>32.82750005722046</v>
       </c>
       <c r="K2">
-        <v>30.059000053405761</v>
+        <v>30.05900005340576</v>
       </c>
       <c r="L2">
         <v>25.30174999237061</v>
@@ -851,7 +795,7 @@
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>1.1299999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -868,7 +812,7 @@
       <c r="T2">
         <v>12.22222222222222</v>
       </c>
-      <c r="U2" s="3" t="b">
+      <c r="U2" t="b">
         <v>1</v>
       </c>
       <c r="V2" t="b">
@@ -878,25 +822,25 @@
         <v>1</v>
       </c>
       <c r="X2">
-        <v>18.399999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="Y2">
-        <v>35.950000000000003</v>
+        <v>35.95</v>
       </c>
       <c r="Z2">
         <v>45.11</v>
       </c>
       <c r="AD2">
-        <v>6.8320000000000007</v>
+        <v>6.832000000000001</v>
       </c>
       <c r="AH2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>65</v>
       </c>
       <c r="AJ2" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="AK2">
         <v>0.7</v>
@@ -905,21 +849,21 @@
         <v>1.27</v>
       </c>
       <c r="AM2">
-        <v>81.430000000000007</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AN2">
-        <v>587.79999999999995</v>
+        <v>587.8</v>
       </c>
       <c r="AO2">
-        <v>75.292222961809657</v>
+        <v>75.29222296180966</v>
       </c>
     </row>
     <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B3">
-        <v>89.660377358490564</v>
+        <v>89.66037735849056</v>
       </c>
       <c r="C3">
         <v>126</v>
@@ -937,19 +881,19 @@
         <v>5.55</v>
       </c>
       <c r="H3">
-        <v>0.17573251346648261</v>
+        <v>0.1757325134664826</v>
       </c>
       <c r="I3">
         <v>3.5739999294281</v>
       </c>
       <c r="J3">
-        <v>3.5074999690055848</v>
+        <v>3.507499969005585</v>
       </c>
       <c r="K3">
-        <v>3.3695999860763548</v>
+        <v>3.369599986076355</v>
       </c>
       <c r="L3">
-        <v>2.9455499970912928</v>
+        <v>2.945549997091293</v>
       </c>
       <c r="M3">
         <v>1.02</v>
@@ -982,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="Y3">
         <v>4.07</v>
@@ -991,16 +935,16 @@
         <v>30.11</v>
       </c>
       <c r="AD3">
-        <v>3.0150001999999998</v>
+        <v>3.0150002</v>
       </c>
       <c r="AH3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI3" s="5" t="s">
-        <v>47</v>
+        <v>59</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>66</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="AK3">
         <v>0.05</v>
@@ -1015,15 +959,15 @@
         <v>55.2</v>
       </c>
       <c r="AO3">
-        <v>74.098018855603257</v>
+        <v>74.09801885560326</v>
       </c>
     </row>
     <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4">
-        <v>91.547169811320757</v>
+        <v>91.54716981132076</v>
       </c>
       <c r="C4">
         <v>17</v>
@@ -1035,22 +979,22 @@
         <v>2.34</v>
       </c>
       <c r="F4">
-        <v>-0.84386290178191414</v>
+        <v>-0.8438629017819141</v>
       </c>
       <c r="G4">
         <v>2.7</v>
       </c>
       <c r="H4">
-        <v>-0.85255737511456708</v>
+        <v>-0.8525573751145671</v>
       </c>
       <c r="I4">
         <v>30.70999984741211</v>
       </c>
       <c r="J4">
-        <v>29.722500133514409</v>
+        <v>29.72250013351441</v>
       </c>
       <c r="K4">
-        <v>27.835000038146969</v>
+        <v>27.83500003814697</v>
       </c>
       <c r="L4">
         <v>20.12639998435974</v>
@@ -1059,7 +1003,7 @@
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1074,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>14.444444444444439</v>
+        <v>14.44444444444444</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -1095,22 +1039,22 @@
         <v>794.27</v>
       </c>
       <c r="AD4">
-        <v>11.476000000000001</v>
+        <v>11.476</v>
       </c>
       <c r="AH4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI4" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
       </c>
       <c r="AJ4" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="AK4">
         <v>0.9</v>
       </c>
       <c r="AL4">
-        <v>1.1299999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AM4">
         <v>25.56</v>
@@ -1119,15 +1063,15 @@
         <v>38.9</v>
       </c>
       <c r="AO4">
-        <v>59.666553909093857</v>
+        <v>59.66655390909386</v>
       </c>
     </row>
     <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B5">
-        <v>85.320754716981128</v>
+        <v>85.32075471698113</v>
       </c>
       <c r="C5">
         <v>297</v>
@@ -1139,13 +1083,13 @@
         <v>4.08</v>
       </c>
       <c r="F5">
-        <v>0.64105468505383922</v>
+        <v>0.6410546850538392</v>
       </c>
       <c r="G5">
         <v>4.46</v>
       </c>
       <c r="H5">
-        <v>-0.21754326848205921</v>
+        <v>-0.2175432684820592</v>
       </c>
       <c r="I5">
         <v>26.64999961853027</v>
@@ -1154,16 +1098,16 @@
         <v>25.23999996185303</v>
       </c>
       <c r="K5">
-        <v>23.065400009155269</v>
+        <v>23.06540000915527</v>
       </c>
       <c r="L5">
-        <v>19.681649966239931</v>
+        <v>19.68164996623993</v>
       </c>
       <c r="M5">
         <v>1.06</v>
       </c>
       <c r="N5">
-        <v>1.1599999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1199,16 +1143,16 @@
         <v>12.73</v>
       </c>
       <c r="AD5">
-        <v>4.1820000000000004</v>
+        <v>4.182</v>
       </c>
       <c r="AH5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI5" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>65</v>
       </c>
       <c r="AJ5" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="AK5">
         <v>0.06</v>
@@ -1223,15 +1167,15 @@
         <v>127.4</v>
       </c>
       <c r="AO5">
-        <v>58.586713462315579</v>
+        <v>58.58671346231558</v>
       </c>
     </row>
     <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B6">
-        <v>90.377358490566039</v>
+        <v>90.37735849056604</v>
       </c>
       <c r="C6">
         <v>266</v>
@@ -1243,25 +1187,25 @@
         <v>3.81</v>
       </c>
       <c r="F6">
-        <v>0.41063643882070511</v>
+        <v>0.4106364388207051</v>
       </c>
       <c r="G6">
         <v>4.32</v>
       </c>
       <c r="H6">
-        <v>-0.26805575423691769</v>
+        <v>-0.2680557542369177</v>
       </c>
       <c r="I6">
-        <v>6.4379999160766603</v>
+        <v>6.43799991607666</v>
       </c>
       <c r="J6">
-        <v>6.2554999351501461</v>
+        <v>6.255499935150146</v>
       </c>
       <c r="K6">
-        <v>5.5225999832153319</v>
+        <v>5.522599983215332</v>
       </c>
       <c r="L6">
-        <v>4.4035499870777128</v>
+        <v>4.403549987077713</v>
       </c>
       <c r="M6">
         <v>1.03</v>
@@ -1303,19 +1247,19 @@
         <v>8.26</v>
       </c>
       <c r="AD6">
-        <v>3.6520000000000001</v>
+        <v>3.652</v>
       </c>
       <c r="AH6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
       </c>
       <c r="AJ6" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="AK6">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AL6">
         <v>0.4</v>
@@ -1327,15 +1271,15 @@
         <v>453.9</v>
       </c>
       <c r="AO6">
-        <v>55.697035810357562</v>
+        <v>55.69703581035756</v>
       </c>
     </row>
     <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B7">
-        <v>87.509433962264154</v>
+        <v>87.50943396226415</v>
       </c>
       <c r="C7">
         <v>735</v>
@@ -1344,16 +1288,16 @@
         <v>3.62</v>
       </c>
       <c r="E7">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="F7" s="2">
-        <v>-1.1084171844940309</v>
+        <v>2.03</v>
+      </c>
+      <c r="F7">
+        <v>-1.108417184494031</v>
       </c>
       <c r="G7">
         <v>3.91</v>
       </c>
       <c r="H7">
-        <v>-0.41598517680471792</v>
+        <v>-0.4159851768047179</v>
       </c>
       <c r="I7">
         <v>3.621999931335449</v>
@@ -1362,16 +1306,16 @@
         <v>3.479499995708466</v>
       </c>
       <c r="K7">
-        <v>3.2884000015258792</v>
+        <v>3.288400001525879</v>
       </c>
       <c r="L7">
-        <v>3.1100500059127811</v>
+        <v>3.110050005912781</v>
       </c>
       <c r="M7">
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1401,22 +1345,22 @@
         <v>0.95</v>
       </c>
       <c r="Y7">
-        <v>4.0599999999999996</v>
+        <v>4.06</v>
       </c>
       <c r="Z7">
         <v>3.07</v>
       </c>
       <c r="AD7">
-        <v>26.068999999999999</v>
+        <v>26.069</v>
       </c>
       <c r="AH7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI7" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>68</v>
       </c>
       <c r="AJ7" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="AK7">
         <v>0.18</v>
@@ -1425,21 +1369,21 @@
         <v>0.42</v>
       </c>
       <c r="AM7">
-        <v>133.33000000000001</v>
+        <v>133.33</v>
       </c>
       <c r="AN7">
-        <v>160.69999999999999</v>
+        <v>160.7</v>
       </c>
       <c r="AO7">
-        <v>43.021685237338922</v>
+        <v>43.02168523733892</v>
       </c>
     </row>
     <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B8">
-        <v>92.754716981132077</v>
+        <v>92.75471698113208</v>
       </c>
       <c r="C8">
         <v>483</v>
@@ -1451,25 +1395,25 @@
         <v>3.16</v>
       </c>
       <c r="F8">
-        <v>-0.14407415396276591</v>
+        <v>-0.1440741539627659</v>
       </c>
       <c r="G8">
         <v>4.68</v>
       </c>
       <c r="H8">
-        <v>-0.13816650515299581</v>
+        <v>-0.1381665051529958</v>
       </c>
       <c r="I8">
-        <v>31.120000076293941</v>
+        <v>31.12000007629394</v>
       </c>
       <c r="J8">
-        <v>29.190000057220459</v>
+        <v>29.19000005722046</v>
       </c>
       <c r="K8">
-        <v>26.085999946594239</v>
+        <v>26.08599994659424</v>
       </c>
       <c r="L8">
-        <v>20.281699976921079</v>
+        <v>20.28169997692108</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -1508,19 +1452,19 @@
         <v>34</v>
       </c>
       <c r="Z8">
-        <v>38.340000000000003</v>
+        <v>38.34</v>
       </c>
       <c r="AD8">
         <v>15.464</v>
       </c>
       <c r="AH8" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>69</v>
       </c>
       <c r="AJ8" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="AK8">
         <v>0.53</v>
@@ -1535,15 +1479,15 @@
         <v>175.5</v>
       </c>
       <c r="AO8">
-        <v>40.674359262671857</v>
+        <v>40.67435926267186</v>
       </c>
     </row>
     <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B9">
-        <v>87.433962264150949</v>
+        <v>87.43396226415095</v>
       </c>
       <c r="C9">
         <v>591</v>
@@ -1555,31 +1499,31 @@
         <v>2.7</v>
       </c>
       <c r="F9">
-        <v>-0.53663857347106847</v>
+        <v>-0.5366385734710685</v>
       </c>
       <c r="G9">
         <v>3.76</v>
       </c>
       <c r="H9">
-        <v>-0.47010569725635221</v>
+        <v>-0.4701056972563522</v>
       </c>
       <c r="I9">
         <v>561</v>
       </c>
       <c r="J9">
-        <v>539.42499999999995</v>
+        <v>539.425</v>
       </c>
       <c r="K9">
-        <v>511.83800048828118</v>
+        <v>511.8380004882812</v>
       </c>
       <c r="L9">
-        <v>414.15500045776372</v>
+        <v>414.1550004577637</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1615,16 +1559,16 @@
         <v>361.37</v>
       </c>
       <c r="AD9">
-        <v>11.364000000000001</v>
+        <v>11.364</v>
       </c>
       <c r="AH9" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI9" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>70</v>
       </c>
       <c r="AJ9" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AK9">
         <v>22.09</v>
@@ -1644,10 +1588,10 @@
     </row>
     <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B10">
-        <v>86.339622641509436</v>
+        <v>86.33962264150944</v>
       </c>
       <c r="C10">
         <v>187</v>
@@ -1656,28 +1600,28 @@
         <v>21.3</v>
       </c>
       <c r="E10">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="F10" s="2">
+        <v>2.07</v>
+      </c>
+      <c r="F10">
         <v>-1.074281148015048</v>
       </c>
       <c r="G10">
         <v>3.65</v>
       </c>
       <c r="H10">
-        <v>-0.50979407892088391</v>
+        <v>-0.5097940789208839</v>
       </c>
       <c r="I10">
-        <v>21.339999771118169</v>
+        <v>21.33999977111817</v>
       </c>
       <c r="J10">
-        <v>20.556999969482419</v>
+        <v>20.55699996948242</v>
       </c>
       <c r="K10">
-        <v>19.982199974060059</v>
+        <v>19.98219997406006</v>
       </c>
       <c r="L10">
-        <v>18.446199965476989</v>
+        <v>18.44619996547699</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -1722,13 +1666,13 @@
         <v>211600</v>
       </c>
       <c r="AH10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI10" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>70</v>
       </c>
       <c r="AJ10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="AK10">
         <v>1.02</v>
@@ -1743,45 +1687,45 @@
         <v>209.1</v>
       </c>
       <c r="AO10">
-        <v>39.971591856051653</v>
+        <v>39.97159185605165</v>
       </c>
     </row>
     <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>90.339622641509436</v>
+        <v>90.33962264150944</v>
       </c>
       <c r="C11">
         <v>201</v>
       </c>
       <c r="D11">
-        <v>71.650000000000006</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="E11">
         <v>2.75</v>
       </c>
       <c r="F11">
-        <v>-0.49396852787234002</v>
+        <v>-0.49396852787234</v>
       </c>
       <c r="G11">
         <v>3.95</v>
       </c>
       <c r="H11">
-        <v>-0.40155303801761538</v>
+        <v>-0.4015530380176154</v>
       </c>
       <c r="I11">
-        <v>68.509999084472653</v>
+        <v>68.50999908447265</v>
       </c>
       <c r="J11">
-        <v>64.825000190734869</v>
+        <v>64.82500019073487</v>
       </c>
       <c r="K11">
-        <v>57.506000366210941</v>
+        <v>57.50600036621094</v>
       </c>
       <c r="L11">
-        <v>48.789000148773191</v>
+        <v>48.78900014877319</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -1814,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="X11">
-        <v>33.299999999999997</v>
+        <v>33.3</v>
       </c>
       <c r="Y11">
         <v>75.5</v>
@@ -1823,16 +1767,16 @@
         <v>77.84</v>
       </c>
       <c r="AD11">
-        <v>7.8660004000000008</v>
+        <v>7.866000400000001</v>
       </c>
       <c r="AH11" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI11" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
       </c>
       <c r="AJ11" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="AK11">
         <v>1.71</v>
@@ -1841,21 +1785,21 @@
         <v>2.94</v>
       </c>
       <c r="AM11">
-        <v>71.930000000000007</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="AN11">
         <v>147.1</v>
       </c>
       <c r="AO11">
-        <v>39.064584276049153</v>
+        <v>39.06458427604915</v>
       </c>
     </row>
     <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B12">
-        <v>83.584905660377359</v>
+        <v>83.58490566037736</v>
       </c>
       <c r="C12">
         <v>234</v>
@@ -1876,22 +1820,22 @@
         <v>-0.3835128645337374</v>
       </c>
       <c r="I12">
-        <v>6.0019999504089352</v>
+        <v>6.001999950408935</v>
       </c>
       <c r="J12">
-        <v>5.4619999647140496</v>
+        <v>5.46199996471405</v>
       </c>
       <c r="K12">
-        <v>5.4183999824523923</v>
+        <v>5.418399982452392</v>
       </c>
       <c r="L12">
-        <v>5.0799999976158139</v>
+        <v>5.079999997615814</v>
       </c>
       <c r="M12">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>1.1100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1927,16 +1871,16 @@
         <v>14.97</v>
       </c>
       <c r="AD12">
-        <v>6.9290000000000003</v>
+        <v>6.929</v>
       </c>
       <c r="AH12" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI12" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>67</v>
       </c>
       <c r="AJ12" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="AK12">
         <v>0.45</v>
@@ -1951,12 +1895,12 @@
         <v>146.5</v>
       </c>
       <c r="AO12">
-        <v>36.052748608049313</v>
+        <v>36.05274860804931</v>
       </c>
     </row>
     <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <v>96</v>
@@ -1970,7 +1914,7 @@
       <c r="E13">
         <v>6.01</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13">
         <v>2.28811844516476</v>
       </c>
       <c r="G13">
@@ -1980,16 +1924,16 @@
         <v>1.788524022925182</v>
       </c>
       <c r="I13">
-        <v>3.2300000190734859</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="J13">
-        <v>3.0444999933242798</v>
+        <v>3.04449999332428</v>
       </c>
       <c r="K13">
-        <v>2.7708000040054319</v>
+        <v>2.770800004005432</v>
       </c>
       <c r="L13">
-        <v>2.6697999978065492</v>
+        <v>2.669799997806549</v>
       </c>
       <c r="M13">
         <v>1.06</v>
@@ -2031,16 +1975,16 @@
         <v>1.51</v>
       </c>
       <c r="AD13">
-        <v>2.2010000000000001</v>
+        <v>2.201</v>
       </c>
       <c r="AH13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI13" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>71</v>
       </c>
       <c r="AJ13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AK13">
         <v>0.08</v>
@@ -2055,15 +1999,15 @@
         <v>9.4</v>
       </c>
       <c r="AO13">
-        <v>30.767052175074749</v>
+        <v>30.76705217507475</v>
       </c>
     </row>
     <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B14">
-        <v>81.283018867924525</v>
+        <v>81.28301886792453</v>
       </c>
       <c r="C14">
         <v>228</v>
@@ -2081,19 +2025,19 @@
         <v>4.28</v>
       </c>
       <c r="H14">
-        <v>-0.28248789302402022</v>
+        <v>-0.2824878930240202</v>
       </c>
       <c r="I14">
-        <v>19.809999465942379</v>
+        <v>19.80999946594238</v>
       </c>
       <c r="J14">
-        <v>19.210999774932858</v>
+        <v>19.21099977493286</v>
       </c>
       <c r="K14">
-        <v>18.470000038146971</v>
+        <v>18.47000003814697</v>
       </c>
       <c r="L14">
-        <v>17.635849986076359</v>
+        <v>17.63584998607636</v>
       </c>
       <c r="M14">
         <v>1.03</v>
@@ -2135,16 +2079,16 @@
         <v>45.29</v>
       </c>
       <c r="AD14">
-        <v>9.0730000000000004</v>
+        <v>9.073</v>
       </c>
       <c r="AH14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI14" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>70</v>
       </c>
       <c r="AJ14" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AK14">
         <v>0.77</v>
@@ -2153,21 +2097,21 @@
         <v>1.48</v>
       </c>
       <c r="AM14">
-        <v>92.21</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="AN14">
         <v>21.9</v>
       </c>
       <c r="AO14">
-        <v>30.562829641352639</v>
+        <v>30.56282964135264</v>
       </c>
     </row>
     <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B15">
-        <v>98.150943396226424</v>
+        <v>98.15094339622642</v>
       </c>
       <c r="C15">
         <v>136</v>
@@ -2176,19 +2120,19 @@
         <v>15.82</v>
       </c>
       <c r="E15">
-        <v>4.9400000000000004</v>
+        <v>4.94</v>
       </c>
       <c r="F15">
-        <v>1.3749794693519699</v>
+        <v>1.37497946935197</v>
       </c>
       <c r="G15">
         <v>13.82</v>
       </c>
-      <c r="H15" s="6">
-        <v>3.1595772076999151</v>
+      <c r="H15">
+        <v>3.159577207699915</v>
       </c>
       <c r="I15">
-        <v>15.756000137329099</v>
+        <v>15.7560001373291</v>
       </c>
       <c r="J15">
         <v>15.49800000190735</v>
@@ -2239,19 +2183,19 @@
         <v>173</v>
       </c>
       <c r="AD15">
-        <v>7.7470005000000004</v>
+        <v>7.7470005</v>
       </c>
       <c r="AH15" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI15" s="5" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>72</v>
       </c>
       <c r="AJ15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AK15">
-        <v>1.0900000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="AL15">
         <v>1.31</v>
@@ -2263,15 +2207,15 @@
         <v>43.4</v>
       </c>
       <c r="AO15">
-        <v>25.606500802897362</v>
+        <v>25.60650080289736</v>
       </c>
     </row>
     <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B16">
-        <v>93.547169811320757</v>
+        <v>93.54716981132076</v>
       </c>
       <c r="C16">
         <v>276</v>
@@ -2292,16 +2236,16 @@
         <v>0.1576923399826046</v>
       </c>
       <c r="I16">
-        <v>46.179999542236331</v>
+        <v>46.17999954223633</v>
       </c>
       <c r="J16">
-        <v>43.702499961853029</v>
+        <v>43.70249996185303</v>
       </c>
       <c r="K16">
-        <v>38.660000038146983</v>
+        <v>38.66000003814698</v>
       </c>
       <c r="L16">
-        <v>38.009999990463257</v>
+        <v>38.00999999046326</v>
       </c>
       <c r="M16">
         <v>1.06</v>
@@ -2343,16 +2287,16 @@
         <v>56.37</v>
       </c>
       <c r="AD16">
-        <v>26.751999999999999</v>
+        <v>26.752</v>
       </c>
       <c r="AH16" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI16" s="4" t="s">
         <v>64</v>
       </c>
+      <c r="AI16" t="s">
+        <v>70</v>
+      </c>
       <c r="AJ16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AK16">
         <v>1.92</v>
@@ -2367,15 +2311,15 @@
         <v>9</v>
       </c>
       <c r="AO16">
-        <v>23.004554602379791</v>
+        <v>23.00455460237979</v>
       </c>
     </row>
     <row r="17" spans="1:41">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B17">
-        <v>81.698113207547181</v>
+        <v>81.69811320754718</v>
       </c>
       <c r="C17">
         <v>492</v>
@@ -2387,7 +2331,7 @@
         <v>2.29</v>
       </c>
       <c r="F17">
-        <v>-0.88653294738064259</v>
+        <v>-0.8865329473806426</v>
       </c>
       <c r="G17">
         <v>2.69</v>
@@ -2396,16 +2340,16 @@
         <v>-0.8561654098113427</v>
       </c>
       <c r="I17">
-        <v>11.415999984741211</v>
+        <v>11.41599998474121</v>
       </c>
       <c r="J17">
-        <v>11.075999927520749</v>
+        <v>11.07599992752075</v>
       </c>
       <c r="K17">
-        <v>10.723800010681151</v>
+        <v>10.72380001068115</v>
       </c>
       <c r="L17">
-        <v>9.5015000009536745</v>
+        <v>9.501500000953675</v>
       </c>
       <c r="M17">
         <v>1.03</v>
@@ -2450,13 +2394,13 @@
         <v>23.163</v>
       </c>
       <c r="AH17" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI17" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>69</v>
       </c>
       <c r="AJ17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK17">
         <v>1.71</v>
@@ -2468,18 +2412,18 @@
         <v>6.43</v>
       </c>
       <c r="AN17">
-        <v>16.100000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="AO17">
-        <v>14.557090233308379</v>
+        <v>14.55709023330838</v>
       </c>
     </row>
     <row r="18" spans="1:41">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B18">
-        <v>86.528301886792462</v>
+        <v>86.52830188679246</v>
       </c>
       <c r="C18">
         <v>179</v>
@@ -2491,31 +2435,31 @@
         <v>3.78</v>
       </c>
       <c r="F18">
-        <v>0.38503441146146777</v>
+        <v>0.3850344114614678</v>
       </c>
       <c r="G18">
-        <v>4.5199999999999996</v>
+        <v>4.52</v>
       </c>
       <c r="H18">
-        <v>-0.19589506030140569</v>
+        <v>-0.1958950603014057</v>
       </c>
       <c r="I18">
-        <v>39.620000457763673</v>
+        <v>39.62000045776367</v>
       </c>
       <c r="J18">
-        <v>38.582500076293947</v>
+        <v>38.58250007629395</v>
       </c>
       <c r="K18">
-        <v>34.816999893188473</v>
+        <v>34.81699989318847</v>
       </c>
       <c r="L18">
-        <v>32.054749956130983</v>
+        <v>32.05474995613098</v>
       </c>
       <c r="M18">
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>1.1399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2548,19 +2492,19 @@
         <v>43.45</v>
       </c>
       <c r="Z18">
-        <v>88.21</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AD18">
-        <v>14.326000000000001</v>
+        <v>14.326</v>
       </c>
       <c r="AH18" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI18" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>67</v>
       </c>
       <c r="AJ18" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="AK18">
         <v>1.92</v>
@@ -2579,7 +2523,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>